--- a/data/processed/positivacao/2022-09_positivacao_anonimizado.xlsx
+++ b/data/processed/positivacao/2022-09_positivacao_anonimizado.xlsx
@@ -551,7 +551,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vendedor: 1 - ROBSON</t>
+          <t>Vendedor: 1 - VENDEDOR 01</t>
         </is>
       </c>
       <c r="B8" t="inlineStr"/>
@@ -25387,7 +25387,7 @@
     <row r="964">
       <c r="A964" t="inlineStr">
         <is>
-          <t>Vendedor: 3 - FERNANDA</t>
+          <t>Vendedor: 3 - VENDEDOR 03</t>
         </is>
       </c>
       <c r="B964" t="inlineStr"/>
@@ -36687,7 +36687,7 @@
     <row r="1399">
       <c r="A1399" t="inlineStr">
         <is>
-          <t>Vendedor: 4 - DANIELA</t>
+          <t>Vendedor: 4 - VENDEDOR 04</t>
         </is>
       </c>
       <c r="B1399" t="inlineStr"/>
@@ -65657,7 +65657,7 @@
     <row r="2514">
       <c r="A2514" t="inlineStr">
         <is>
-          <t>Vendedor: 8 - RAFAEL</t>
+          <t>Vendedor: 8 - VENDEDOR 08</t>
         </is>
       </c>
       <c r="B2514" t="inlineStr"/>
@@ -67328,12 +67328,12 @@
       <c r="A2579" t="inlineStr"/>
       <c r="B2579" t="inlineStr">
         <is>
-          <t>Vendedor 1 - ROBSON: positivou 14 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 50.516,07
+          <t>Vendedor 1 - VENDEDOR 01: positivou 14 cliente(s), não positivou 86 cliente(s) - Total vendido: R$ 50.516,07
 Vendedor 18 - LOJA: positivou 113 cliente(s), não positivou 741 cliente(s) - Total vendido: R$ 88.400,55
-Vendedor 3 - FERNANDA: positivou 97 cliente(s), não positivou 337 cliente(s) - Total vendido: R$ 140.247,49
-Vendedor 4 - DANIELA: positivou 46 cliente(s), não positivou 615 cliente(s) - Total vendido: R$ 31.040,89
+Vendedor 3 - VENDEDOR 03: positivou 97 cliente(s), não positivou 337 cliente(s) - Total vendido: R$ 140.247,49
+Vendedor 4 - VENDEDOR 04: positivou 46 cliente(s), não positivou 615 cliente(s) - Total vendido: R$ 31.040,89
 Vendedor 5 - SITE: positivou 13 cliente(s), não positivou 439 cliente(s) - Total vendido: R$ 1.387,74
-Vendedor 8 - RAFAEL: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
+Vendedor 8 - VENDEDOR 08: positivou 0 cliente(s), não positivou 63 cliente(s) - Total vendido: R$ 0,00</t>
         </is>
       </c>
       <c r="C2579" t="inlineStr"/>
